--- a/1-code/ruwen/figure/network_table_c.xlsx
+++ b/1-code/ruwen/figure/network_table_c.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qd/Desktop/helios/HELIOS-project/1-code/ruwen/figure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67782541-3FB4-A942-AE43-836D9210E2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04ECFFF2-C474-3D48-BA1E-0A3BB54BF65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="21800" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="500" windowWidth="21800" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="74">
   <si>
     <t>from</t>
   </si>
@@ -239,6 +239,10 @@
   </si>
   <si>
     <t>Streptococcus agalactiae</t>
+  </si>
+  <si>
+    <t>Eggerthella guodeyinii</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -274,12 +278,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -294,12 +304,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -851,32 +862,32 @@
         <v>2.513021969751732</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:9" s="3" customFormat="1">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>0.57807768585948527</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>3.523782965237861E-3</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="G9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="3">
         <v>0.57807768585948527</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="3">
         <v>2.4529908482458662</v>
       </c>
     </row>
@@ -1025,32 +1036,32 @@
         <v>3.146176268677674</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:9" s="3" customFormat="1">
+      <c r="A15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-0.51004387289848963</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.416094748436926E-2</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="2">
-        <v>-0.51004387289848963</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1.416094748436926E-2</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <v>0.51004387289848963</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="3">
         <v>1.8489076877855859</v>
       </c>
     </row>
